--- a/Edgar_Tools/10k_balance_sheets_2014-2024_cleaned.xlsx
+++ b/Edgar_Tools/10k_balance_sheets_2014-2024_cleaned.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vermouth/Documents/GitHub/Data-Analysis-Projects/Edgar_Tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C940363-7FE7-8D46-8CC8-F3B717B4F3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E55C315-3625-6740-B75E-C5A973717476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="143">
   <si>
     <t>label</t>
   </si>
@@ -206,6 +208,249 @@
   </si>
   <si>
     <t>use VLOOKUP to fil in the information</t>
+  </si>
+  <si>
+    <t>Sep 28, 2024</t>
+  </si>
+  <si>
+    <t>Sep 30, 2023</t>
+  </si>
+  <si>
+    <t>$29,943</t>
+  </si>
+  <si>
+    <t>$29,965</t>
+  </si>
+  <si>
+    <t>$35,228</t>
+  </si>
+  <si>
+    <t>$31,590</t>
+  </si>
+  <si>
+    <t>$33,410</t>
+  </si>
+  <si>
+    <t>$29,508</t>
+  </si>
+  <si>
+    <t>$32,833</t>
+  </si>
+  <si>
+    <t>$31,477</t>
+  </si>
+  <si>
+    <t>$7,286</t>
+  </si>
+  <si>
+    <t>$6,331</t>
+  </si>
+  <si>
+    <t>$14,287</t>
+  </si>
+  <si>
+    <t>$14,695</t>
+  </si>
+  <si>
+    <t>$152,987</t>
+  </si>
+  <si>
+    <t>$143,566</t>
+  </si>
+  <si>
+    <t>$91,479</t>
+  </si>
+  <si>
+    <t>$100,544</t>
+  </si>
+  <si>
+    <t>$45,680</t>
+  </si>
+  <si>
+    <t>$43,715</t>
+  </si>
+  <si>
+    <t>$74,834</t>
+  </si>
+  <si>
+    <t>$64,758</t>
+  </si>
+  <si>
+    <t>$211,993</t>
+  </si>
+  <si>
+    <t>$209,017</t>
+  </si>
+  <si>
+    <t>$364,980</t>
+  </si>
+  <si>
+    <t>$352,583</t>
+  </si>
+  <si>
+    <t>$68,960</t>
+  </si>
+  <si>
+    <t>$62,611</t>
+  </si>
+  <si>
+    <t>$78,304</t>
+  </si>
+  <si>
+    <t>$58,829</t>
+  </si>
+  <si>
+    <t>$8,249</t>
+  </si>
+  <si>
+    <t>$8,061</t>
+  </si>
+  <si>
+    <t>$9,967</t>
+  </si>
+  <si>
+    <t>$5,985</t>
+  </si>
+  <si>
+    <t>$10,912</t>
+  </si>
+  <si>
+    <t>$9,822</t>
+  </si>
+  <si>
+    <t>$176,392</t>
+  </si>
+  <si>
+    <t>$145,308</t>
+  </si>
+  <si>
+    <t>$85,750</t>
+  </si>
+  <si>
+    <t>$95,281</t>
+  </si>
+  <si>
+    <t>$45,888</t>
+  </si>
+  <si>
+    <t>$49,848</t>
+  </si>
+  <si>
+    <t>$131,638</t>
+  </si>
+  <si>
+    <t>$145,129</t>
+  </si>
+  <si>
+    <t>$308,030</t>
+  </si>
+  <si>
+    <t>$290,437</t>
+  </si>
+  <si>
+    <t>$83,276</t>
+  </si>
+  <si>
+    <t>$73,812</t>
+  </si>
+  <si>
+    <t>$(19,154)</t>
+  </si>
+  <si>
+    <t>$(214)</t>
+  </si>
+  <si>
+    <t>$(7,172)</t>
+  </si>
+  <si>
+    <t>$(11,452)</t>
+  </si>
+  <si>
+    <t>$56,950</t>
+  </si>
+  <si>
+    <t>$62,146</t>
+  </si>
+  <si>
+    <t>Sep 24, 2022</t>
+  </si>
+  <si>
+    <t>$23,646</t>
+  </si>
+  <si>
+    <t>$24,658</t>
+  </si>
+  <si>
+    <t>$28,184</t>
+  </si>
+  <si>
+    <t>$4,946</t>
+  </si>
+  <si>
+    <t>$32,748</t>
+  </si>
+  <si>
+    <t>$21,223</t>
+  </si>
+  <si>
+    <t>$135,405</t>
+  </si>
+  <si>
+    <t>$120,805</t>
+  </si>
+  <si>
+    <t>$42,117</t>
+  </si>
+  <si>
+    <t>$54,428</t>
+  </si>
+  <si>
+    <t>$217,350</t>
+  </si>
+  <si>
+    <t>$352,755</t>
+  </si>
+  <si>
+    <t>$64,115</t>
+  </si>
+  <si>
+    <t>$60,845</t>
+  </si>
+  <si>
+    <t>$7,912</t>
+  </si>
+  <si>
+    <t>$9,982</t>
+  </si>
+  <si>
+    <t>$11,128</t>
+  </si>
+  <si>
+    <t>$153,982</t>
+  </si>
+  <si>
+    <t>$98,959</t>
+  </si>
+  <si>
+    <t>$49,142</t>
+  </si>
+  <si>
+    <t>$148,101</t>
+  </si>
+  <si>
+    <t>$302,083</t>
+  </si>
+  <si>
+    <t>$64,849</t>
+  </si>
+  <si>
+    <t>$(3,068)</t>
+  </si>
+  <si>
+    <t>$(11,109)</t>
+  </si>
+  <si>
+    <t>$50,672</t>
   </si>
 </sst>
 </file>
@@ -227,6 +472,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -264,12 +510,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5072,4 +5319,855 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8465D99E-09E5-8248-B806-8FBAF3110E24}">
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="38.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="38.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" t="s">
+        <v>38</v>
+      </c>
+      <c r="H26" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" t="s">
+        <v>103</v>
+      </c>
+      <c r="G27" t="s">
+        <v>39</v>
+      </c>
+      <c r="H27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="G28" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" t="s">
+        <v>107</v>
+      </c>
+      <c r="G29" t="s">
+        <v>41</v>
+      </c>
+      <c r="H29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3">
+        <v>15116786</v>
+      </c>
+      <c r="C31" s="3">
+        <v>15550061</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="G31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3">
+        <v>15116786</v>
+      </c>
+      <c r="C32" s="3">
+        <v>15550061</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="G32" t="s">
+        <v>46</v>
+      </c>
+      <c r="H32" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" t="s">
+        <v>47</v>
+      </c>
+      <c r="H33" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" t="s">
+        <v>109</v>
+      </c>
+      <c r="G34" t="s">
+        <v>48</v>
+      </c>
+      <c r="H34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" t="s">
+        <v>111</v>
+      </c>
+      <c r="G35" t="s">
+        <v>49</v>
+      </c>
+      <c r="H35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" t="s">
+        <v>113</v>
+      </c>
+      <c r="G36" t="s">
+        <v>50</v>
+      </c>
+      <c r="H36" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F720F5E-2D61-D148-8AF1-892E5BF7C6E6}">
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="38.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Edgar_Tools/10k_balance_sheets_2014-2024_cleaned.xlsx
+++ b/Edgar_Tools/10k_balance_sheets_2014-2024_cleaned.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vermouth/Documents/GitHub/Data-Analysis-Projects/Edgar_Tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C3C376-2A6A-EE48-AA87-9B8B355FC2FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9124DF42-CF80-AC4E-81D9-A6D456769AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_data" sheetId="1" r:id="rId1"/>
     <sheet name="Copied from Py" sheetId="2" r:id="rId2"/>
+    <sheet name="Quearterly" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="466">
   <si>
     <t>label</t>
   </si>
@@ -957,6 +959,468 @@
   </si>
   <si>
     <t>Fiscal FY • Source: SEC XBRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                      Sep 28, 2024   Sep 30, 2023  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ASSETS:                                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Current assets:                                                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Cash and Cash Equivalents                          $29,943        $29,965  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Current Marketable Securities                      $35,228        $31,590  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Accounts Receivable                                $33,410        $29,508  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Vendor non-trade receivables                       $32,833        $31,477  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Inventory                                           $7,286         $6,331  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Other Current Assets                               $14,287        $14,695  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Total Current Assets                              $152,987       $143,566  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Non-current assets:                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Non Current Marketable Securities                  $91,479       $100,544  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Property, Plant and Equipment                      $45,680        $43,715  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Other Non Current Assets                           $74,834        $64,758  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Total Non Current Assets                          $211,993       $209,017  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Total Assets                                        $364,980       $352,583  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    LIABILITIES AND SHAREHOLDERS’ EQUITY:                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Current liabilities:                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Accounts Payable                                   $68,960        $62,611  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Other Current Liabilities                          $78,304        $58,829  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Deferred revenue                                    $8,249         $8,061  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Commercial paper                                    $9,967         $5,985  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Short Term Debt                                    $10,912         $9,822  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Total Current Liabilities                         $176,392       $145,308  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Non-current liabilities:                                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Long Term Debt                                     $85,750        $95,281  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Other Non Current Liabilities                      $45,888        $49,848  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Total Non Current Liabilities                     $131,638       $145,129  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Total Liabilities                                   $308,030       $290,437  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Commitments and contingencies                                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Common Stock Shares Outstanding                   15,116,786     15,550,061  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Common Stock Shares Issued                        15,116,786     15,550,061  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Shareholders’ equity:                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Common Stock                                       $83,276        $73,812  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Retained Earnings                                $(19,154)         $(214)  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Accumulated Other Comprehensive Income/Loss       $(7,172)      $(11,452)  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Total Stockholders' Equity                         $56,950        $62,146  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Total Liabilities and Stockholders' Equity          $364,980       $352,583  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                           Fiscal FY • Source: SEC XBRL                            </t>
+  </si>
+  <si>
+    <t>Fiscal Q2 • Source: SEC</t>
+  </si>
+  <si>
+    <t>XBRL</t>
+  </si>
+  <si>
+    <t>Fiscal Q1 • Source: SEC</t>
+  </si>
+  <si>
+    <t>Fiscal Q3 • Source: SEC</t>
+  </si>
+  <si>
+    <t>Dec 30, 2023</t>
+  </si>
+  <si>
+    <t>$40,760</t>
+  </si>
+  <si>
+    <t>$32,340</t>
+  </si>
+  <si>
+    <t>$23,194</t>
+  </si>
+  <si>
+    <t>$26,908</t>
+  </si>
+  <si>
+    <t>$6,511</t>
+  </si>
+  <si>
+    <t>$13,979</t>
+  </si>
+  <si>
+    <t>$143,692</t>
+  </si>
+  <si>
+    <t>$99,475</t>
+  </si>
+  <si>
+    <t>$43,666</t>
+  </si>
+  <si>
+    <t>$66,681</t>
+  </si>
+  <si>
+    <t>$209,822</t>
+  </si>
+  <si>
+    <t>$353,514</t>
+  </si>
+  <si>
+    <t>$58,146</t>
+  </si>
+  <si>
+    <t>$54,611</t>
+  </si>
+  <si>
+    <t>$8,264</t>
+  </si>
+  <si>
+    <t>$1,998</t>
+  </si>
+  <si>
+    <t>$10,954</t>
+  </si>
+  <si>
+    <t>$133,973</t>
+  </si>
+  <si>
+    <t>$95,088</t>
+  </si>
+  <si>
+    <t>$50,353</t>
+  </si>
+  <si>
+    <t>$145,441</t>
+  </si>
+  <si>
+    <t>$279,414</t>
+  </si>
+  <si>
+    <t>$75,236</t>
+  </si>
+  <si>
+    <t>$8,242</t>
+  </si>
+  <si>
+    <t>$(9,378)</t>
+  </si>
+  <si>
+    <t>$74,100</t>
+  </si>
+  <si>
+    <t>Fiscal Q1 • Source: SEC XBR</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Jul 1, 2023</t>
+  </si>
+  <si>
+    <t>$28,408</t>
+  </si>
+  <si>
+    <t>$34,074</t>
+  </si>
+  <si>
+    <t>$19,549</t>
+  </si>
+  <si>
+    <t>$7,351</t>
+  </si>
+  <si>
+    <t>$19,637</t>
+  </si>
+  <si>
+    <t>$13,640</t>
+  </si>
+  <si>
+    <t>$122,659</t>
+  </si>
+  <si>
+    <t>$104,061</t>
+  </si>
+  <si>
+    <t>$43,550</t>
+  </si>
+  <si>
+    <t>$64,768</t>
+  </si>
+  <si>
+    <t>$212,379</t>
+  </si>
+  <si>
+    <t>$335,038</t>
+  </si>
+  <si>
+    <t>$46,699</t>
+  </si>
+  <si>
+    <t>$58,897</t>
+  </si>
+  <si>
+    <t>$8,158</t>
+  </si>
+  <si>
+    <t>$3,993</t>
+  </si>
+  <si>
+    <t>$7,216</t>
+  </si>
+  <si>
+    <t>$124,963</t>
+  </si>
+  <si>
+    <t>$98,071</t>
+  </si>
+  <si>
+    <t>$51,730</t>
+  </si>
+  <si>
+    <t>$149,801</t>
+  </si>
+  <si>
+    <t>$274,764</t>
+  </si>
+  <si>
+    <t>$70,667</t>
+  </si>
+  <si>
+    <t>$1,408</t>
+  </si>
+  <si>
+    <t>$(11,801)</t>
+  </si>
+  <si>
+    <t>$60,274</t>
+  </si>
+  <si>
+    <t>Apr 1, 2023</t>
+  </si>
+  <si>
+    <t>$24,687</t>
+  </si>
+  <si>
+    <t>$31,185</t>
+  </si>
+  <si>
+    <t>$17,936</t>
+  </si>
+  <si>
+    <t>$7,482</t>
+  </si>
+  <si>
+    <t>$17,963</t>
+  </si>
+  <si>
+    <t>$13,660</t>
+  </si>
+  <si>
+    <t>$112,913</t>
+  </si>
+  <si>
+    <t>$110,461</t>
+  </si>
+  <si>
+    <t>$43,398</t>
+  </si>
+  <si>
+    <t>$65,388</t>
+  </si>
+  <si>
+    <t>$219,247</t>
+  </si>
+  <si>
+    <t>$332,160</t>
+  </si>
+  <si>
+    <t>$42,945</t>
+  </si>
+  <si>
+    <t>$56,425</t>
+  </si>
+  <si>
+    <t>$8,131</t>
+  </si>
+  <si>
+    <t>$1,996</t>
+  </si>
+  <si>
+    <t>$10,578</t>
+  </si>
+  <si>
+    <t>$120,075</t>
+  </si>
+  <si>
+    <t>$97,041</t>
+  </si>
+  <si>
+    <t>$52,886</t>
+  </si>
+  <si>
+    <t>$149,927</t>
+  </si>
+  <si>
+    <t>$270,002</t>
+  </si>
+  <si>
+    <t>$69,568</t>
+  </si>
+  <si>
+    <t>$4,336</t>
+  </si>
+  <si>
+    <t>$(11,746)</t>
+  </si>
+  <si>
+    <t>$62,158</t>
+  </si>
+  <si>
+    <t>Dec 31, 2022</t>
+  </si>
+  <si>
+    <t>$20,535</t>
+  </si>
+  <si>
+    <t>$30,820</t>
+  </si>
+  <si>
+    <t>$23,752</t>
+  </si>
+  <si>
+    <t>$6,820</t>
+  </si>
+  <si>
+    <t>$30,428</t>
+  </si>
+  <si>
+    <t>$16,422</t>
+  </si>
+  <si>
+    <t>$128,777</t>
+  </si>
+  <si>
+    <t>$114,095</t>
+  </si>
+  <si>
+    <t>$42,951</t>
+  </si>
+  <si>
+    <t>$60,924</t>
+  </si>
+  <si>
+    <t>$217,970</t>
+  </si>
+  <si>
+    <t>$346,747</t>
+  </si>
+  <si>
+    <t>$57,918</t>
+  </si>
+  <si>
+    <t>$59,893</t>
+  </si>
+  <si>
+    <t>$7,992</t>
+  </si>
+  <si>
+    <t>$1,743</t>
+  </si>
+  <si>
+    <t>$9,740</t>
+  </si>
+  <si>
+    <t>$137,286</t>
+  </si>
+  <si>
+    <t>$99,627</t>
+  </si>
+  <si>
+    <t>$53,107</t>
+  </si>
+  <si>
+    <t>$152,734</t>
+  </si>
+  <si>
+    <t>$290,020</t>
+  </si>
+  <si>
+    <t>$66,399</t>
+  </si>
+  <si>
+    <t>$3,240</t>
+  </si>
+  <si>
+    <t>$(12,912)</t>
+  </si>
+  <si>
+    <t>$56,727</t>
   </si>
 </sst>
 </file>
@@ -24026,4 +24490,1422 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98FC7BA0-E2C4-0F4B-ADD2-BCD0C48B7EC4}">
+  <dimension ref="A1:A40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>351</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24DAD562-AC1A-4F41-8C87-B28A52788594}">
+  <dimension ref="A1:O38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="38.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="38.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" t="s">
+        <v>385</v>
+      </c>
+      <c r="J1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K1" t="s">
+        <v>412</v>
+      </c>
+      <c r="N1" t="s">
+        <v>439</v>
+      </c>
+      <c r="O1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G4" t="s">
+        <v>386</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" t="s">
+        <v>117</v>
+      </c>
+      <c r="K4" t="s">
+        <v>413</v>
+      </c>
+      <c r="M4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" t="s">
+        <v>440</v>
+      </c>
+      <c r="O4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5" t="s">
+        <v>387</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>118</v>
+      </c>
+      <c r="K5" t="s">
+        <v>414</v>
+      </c>
+      <c r="M5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" t="s">
+        <v>441</v>
+      </c>
+      <c r="O5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>359</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" t="s">
+        <v>388</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
+        <v>119</v>
+      </c>
+      <c r="K6" t="s">
+        <v>415</v>
+      </c>
+      <c r="M6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" t="s">
+        <v>442</v>
+      </c>
+      <c r="O6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G7" t="s">
+        <v>389</v>
+      </c>
+      <c r="I7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" t="s">
+        <v>120</v>
+      </c>
+      <c r="K7" t="s">
+        <v>416</v>
+      </c>
+      <c r="M7" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" t="s">
+        <v>443</v>
+      </c>
+      <c r="O7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>361</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G8" t="s">
+        <v>390</v>
+      </c>
+      <c r="I8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" t="s">
+        <v>121</v>
+      </c>
+      <c r="K8" t="s">
+        <v>417</v>
+      </c>
+      <c r="M8" t="s">
+        <v>19</v>
+      </c>
+      <c r="N8" t="s">
+        <v>444</v>
+      </c>
+      <c r="O8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>362</v>
+      </c>
+      <c r="C9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G9" t="s">
+        <v>391</v>
+      </c>
+      <c r="I9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>122</v>
+      </c>
+      <c r="K9" t="s">
+        <v>418</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s">
+        <v>445</v>
+      </c>
+      <c r="O9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>363</v>
+      </c>
+      <c r="C10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G10" t="s">
+        <v>392</v>
+      </c>
+      <c r="I10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" t="s">
+        <v>123</v>
+      </c>
+      <c r="K10" t="s">
+        <v>419</v>
+      </c>
+      <c r="M10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" t="s">
+        <v>446</v>
+      </c>
+      <c r="O10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" t="s">
+        <v>124</v>
+      </c>
+      <c r="G12" t="s">
+        <v>393</v>
+      </c>
+      <c r="I12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" t="s">
+        <v>124</v>
+      </c>
+      <c r="K12" t="s">
+        <v>420</v>
+      </c>
+      <c r="M12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12" t="s">
+        <v>447</v>
+      </c>
+      <c r="O12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>365</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13" t="s">
+        <v>394</v>
+      </c>
+      <c r="I13" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" t="s">
+        <v>125</v>
+      </c>
+      <c r="K13" t="s">
+        <v>421</v>
+      </c>
+      <c r="M13" t="s">
+        <v>25</v>
+      </c>
+      <c r="N13" t="s">
+        <v>448</v>
+      </c>
+      <c r="O13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>366</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" t="s">
+        <v>126</v>
+      </c>
+      <c r="G14" t="s">
+        <v>395</v>
+      </c>
+      <c r="I14" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" t="s">
+        <v>126</v>
+      </c>
+      <c r="K14" t="s">
+        <v>422</v>
+      </c>
+      <c r="M14" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" t="s">
+        <v>449</v>
+      </c>
+      <c r="O14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>367</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" t="s">
+        <v>127</v>
+      </c>
+      <c r="G15" t="s">
+        <v>396</v>
+      </c>
+      <c r="I15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" t="s">
+        <v>127</v>
+      </c>
+      <c r="K15" t="s">
+        <v>423</v>
+      </c>
+      <c r="M15" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" t="s">
+        <v>450</v>
+      </c>
+      <c r="O15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>368</v>
+      </c>
+      <c r="C16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" t="s">
+        <v>397</v>
+      </c>
+      <c r="I16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" t="s">
+        <v>128</v>
+      </c>
+      <c r="K16" t="s">
+        <v>424</v>
+      </c>
+      <c r="M16" t="s">
+        <v>28</v>
+      </c>
+      <c r="N16" t="s">
+        <v>451</v>
+      </c>
+      <c r="O16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" t="s">
+        <v>29</v>
+      </c>
+      <c r="M17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>369</v>
+      </c>
+      <c r="C19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" t="s">
+        <v>398</v>
+      </c>
+      <c r="I19" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" t="s">
+        <v>129</v>
+      </c>
+      <c r="K19" t="s">
+        <v>425</v>
+      </c>
+      <c r="M19" t="s">
+        <v>31</v>
+      </c>
+      <c r="N19" t="s">
+        <v>452</v>
+      </c>
+      <c r="O19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s">
+        <v>370</v>
+      </c>
+      <c r="C20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" t="s">
+        <v>399</v>
+      </c>
+      <c r="I20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" t="s">
+        <v>130</v>
+      </c>
+      <c r="K20" t="s">
+        <v>426</v>
+      </c>
+      <c r="M20" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" t="s">
+        <v>453</v>
+      </c>
+      <c r="O20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s">
+        <v>371</v>
+      </c>
+      <c r="C21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" t="s">
+        <v>400</v>
+      </c>
+      <c r="I21" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" t="s">
+        <v>131</v>
+      </c>
+      <c r="K21" t="s">
+        <v>427</v>
+      </c>
+      <c r="M21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N21" t="s">
+        <v>454</v>
+      </c>
+      <c r="O21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>372</v>
+      </c>
+      <c r="C22" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G22" t="s">
+        <v>401</v>
+      </c>
+      <c r="I22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J22" t="s">
+        <v>132</v>
+      </c>
+      <c r="K22" t="s">
+        <v>428</v>
+      </c>
+      <c r="M22" t="s">
+        <v>34</v>
+      </c>
+      <c r="N22" t="s">
+        <v>455</v>
+      </c>
+      <c r="O22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
+        <v>373</v>
+      </c>
+      <c r="C23" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" t="s">
+        <v>133</v>
+      </c>
+      <c r="G23" t="s">
+        <v>402</v>
+      </c>
+      <c r="I23" t="s">
+        <v>35</v>
+      </c>
+      <c r="J23" t="s">
+        <v>133</v>
+      </c>
+      <c r="K23" t="s">
+        <v>429</v>
+      </c>
+      <c r="M23" t="s">
+        <v>35</v>
+      </c>
+      <c r="N23" t="s">
+        <v>456</v>
+      </c>
+      <c r="O23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>374</v>
+      </c>
+      <c r="C24" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="I24" t="s">
+        <v>36</v>
+      </c>
+      <c r="J24" t="s">
+        <v>134</v>
+      </c>
+      <c r="K24" t="s">
+        <v>430</v>
+      </c>
+      <c r="M24" t="s">
+        <v>36</v>
+      </c>
+      <c r="N24" t="s">
+        <v>457</v>
+      </c>
+      <c r="O24" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="I25" t="s">
+        <v>37</v>
+      </c>
+      <c r="M25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" t="s">
+        <v>375</v>
+      </c>
+      <c r="C26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" t="s">
+        <v>135</v>
+      </c>
+      <c r="G26" t="s">
+        <v>404</v>
+      </c>
+      <c r="I26" t="s">
+        <v>38</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="M26" t="s">
+        <v>38</v>
+      </c>
+      <c r="N26" t="s">
+        <v>458</v>
+      </c>
+      <c r="O26" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" t="s">
+        <v>376</v>
+      </c>
+      <c r="C27" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" t="s">
+        <v>136</v>
+      </c>
+      <c r="G27" t="s">
+        <v>405</v>
+      </c>
+      <c r="I27" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="M27" t="s">
+        <v>39</v>
+      </c>
+      <c r="N27" t="s">
+        <v>459</v>
+      </c>
+      <c r="O27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s">
+        <v>377</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="E28" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" t="s">
+        <v>137</v>
+      </c>
+      <c r="G28" t="s">
+        <v>406</v>
+      </c>
+      <c r="I28" t="s">
+        <v>40</v>
+      </c>
+      <c r="J28" t="s">
+        <v>137</v>
+      </c>
+      <c r="K28" t="s">
+        <v>433</v>
+      </c>
+      <c r="M28" t="s">
+        <v>40</v>
+      </c>
+      <c r="N28" t="s">
+        <v>460</v>
+      </c>
+      <c r="O28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" t="s">
+        <v>378</v>
+      </c>
+      <c r="C29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" t="s">
+        <v>138</v>
+      </c>
+      <c r="G29" t="s">
+        <v>407</v>
+      </c>
+      <c r="I29" t="s">
+        <v>41</v>
+      </c>
+      <c r="J29" t="s">
+        <v>138</v>
+      </c>
+      <c r="K29" t="s">
+        <v>434</v>
+      </c>
+      <c r="M29" t="s">
+        <v>41</v>
+      </c>
+      <c r="N29" t="s">
+        <v>461</v>
+      </c>
+      <c r="O29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30" t="s">
+        <v>42</v>
+      </c>
+      <c r="M30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" t="s">
+        <v>45</v>
+      </c>
+      <c r="I31" t="s">
+        <v>45</v>
+      </c>
+      <c r="M31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" t="s">
+        <v>379</v>
+      </c>
+      <c r="C32" t="s">
+        <v>109</v>
+      </c>
+      <c r="E32" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" t="s">
+        <v>139</v>
+      </c>
+      <c r="G32" t="s">
+        <v>408</v>
+      </c>
+      <c r="I32" t="s">
+        <v>46</v>
+      </c>
+      <c r="J32" t="s">
+        <v>139</v>
+      </c>
+      <c r="K32" t="s">
+        <v>435</v>
+      </c>
+      <c r="M32" t="s">
+        <v>46</v>
+      </c>
+      <c r="N32" t="s">
+        <v>462</v>
+      </c>
+      <c r="O32" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" t="s">
+        <v>380</v>
+      </c>
+      <c r="C33" t="s">
+        <v>111</v>
+      </c>
+      <c r="E33" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" t="s">
+        <v>140</v>
+      </c>
+      <c r="G33" t="s">
+        <v>409</v>
+      </c>
+      <c r="I33" t="s">
+        <v>47</v>
+      </c>
+      <c r="J33" t="s">
+        <v>140</v>
+      </c>
+      <c r="K33" t="s">
+        <v>436</v>
+      </c>
+      <c r="M33" t="s">
+        <v>47</v>
+      </c>
+      <c r="N33" t="s">
+        <v>463</v>
+      </c>
+      <c r="O33" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" t="s">
+        <v>381</v>
+      </c>
+      <c r="C34" t="s">
+        <v>113</v>
+      </c>
+      <c r="E34" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" t="s">
+        <v>141</v>
+      </c>
+      <c r="G34" t="s">
+        <v>410</v>
+      </c>
+      <c r="I34" t="s">
+        <v>48</v>
+      </c>
+      <c r="J34" t="s">
+        <v>141</v>
+      </c>
+      <c r="K34" t="s">
+        <v>437</v>
+      </c>
+      <c r="M34" t="s">
+        <v>48</v>
+      </c>
+      <c r="N34" t="s">
+        <v>464</v>
+      </c>
+      <c r="O34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" t="s">
+        <v>382</v>
+      </c>
+      <c r="C35" t="s">
+        <v>115</v>
+      </c>
+      <c r="E35" t="s">
+        <v>49</v>
+      </c>
+      <c r="F35" t="s">
+        <v>142</v>
+      </c>
+      <c r="G35" t="s">
+        <v>411</v>
+      </c>
+      <c r="I35" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" t="s">
+        <v>142</v>
+      </c>
+      <c r="K35" t="s">
+        <v>438</v>
+      </c>
+      <c r="M35" t="s">
+        <v>49</v>
+      </c>
+      <c r="N35" t="s">
+        <v>465</v>
+      </c>
+      <c r="O35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" t="s">
+        <v>368</v>
+      </c>
+      <c r="C36" t="s">
+        <v>87</v>
+      </c>
+      <c r="E36" t="s">
+        <v>50</v>
+      </c>
+      <c r="F36" t="s">
+        <v>128</v>
+      </c>
+      <c r="G36" t="s">
+        <v>397</v>
+      </c>
+      <c r="I36" t="s">
+        <v>50</v>
+      </c>
+      <c r="J36" t="s">
+        <v>128</v>
+      </c>
+      <c r="K36" t="s">
+        <v>424</v>
+      </c>
+      <c r="M36" t="s">
+        <v>50</v>
+      </c>
+      <c r="N36" t="s">
+        <v>451</v>
+      </c>
+      <c r="O36" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>383</v>
+      </c>
+      <c r="B38" t="s">
+        <v>384</v>
+      </c>
+      <c r="E38" t="s">
+        <v>355</v>
+      </c>
+      <c r="F38" t="s">
+        <v>353</v>
+      </c>
+      <c r="I38" t="s">
+        <v>352</v>
+      </c>
+      <c r="J38" t="s">
+        <v>353</v>
+      </c>
+      <c r="M38" t="s">
+        <v>354</v>
+      </c>
+      <c r="N38" t="s">
+        <v>353</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>